--- a/research/CFDL_pack_roadmap_and_model_catalogue.xlsx
+++ b/research/CFDL_pack_roadmap_and_model_catalogue.xlsx
@@ -859,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -876,6 +876,8 @@
     <col width="52" customWidth="1" style="17" min="12" max="13"/>
     <col width="46" customWidth="1" style="17" min="14" max="14"/>
     <col width="14" customWidth="1" style="17" min="15" max="15"/>
+    <col width="16" customWidth="1" style="18" min="16" max="16"/>
+    <col width="13" customWidth="1" style="18" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="18">
@@ -954,6 +956,16 @@
           <t>Link check</t>
         </is>
       </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>Local copy</t>
+        </is>
+      </c>
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>Duplicate of</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="96" customHeight="1" s="18">
       <c r="A2" s="24" t="n">
@@ -8979,6 +8991,4101 @@
           <t>OK — page, video and workbook all obtained 22 August 2026; workbook held locally in cfdl/research</t>
         </is>
       </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate debt — amortization</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>Advanced Amortization Model (v1.1)</t>
+        </is>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr"/>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H109" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J109" s="17" t="inlineStr">
+        <is>
+          <t>Loan amortization schedule with non-standard payment features</t>
+        </is>
+      </c>
+      <c r="K109" s="17" t="inlineStr">
+        <is>
+          <t>A single loan amortized monthly with an annual payment roll-up.</t>
+        </is>
+      </c>
+      <c r="L109" s="17" t="inlineStr">
+        <is>
+          <t>Period-by-period interest/principal split; annual aggregation of a monthly schedule.</t>
+        </is>
+      </c>
+      <c r="M109" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state (balance carried on prev)</t>
+        </is>
+      </c>
+      <c r="N109" s="17" t="inlineStr">
+        <is>
+          <t>Amortization arithmetic against an independent schedule; monthly-to-annual rollup.</t>
+        </is>
+      </c>
+      <c r="O109" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P109" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q109" s="17" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — generic acquisition</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>Basic Real Estate Model (v1.2)</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr"/>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t>Single-sheet acquisition pro forma</t>
+        </is>
+      </c>
+      <c r="K110" s="17" t="inlineStr">
+        <is>
+          <t>A minimal buy/hold/sell on one sheet.</t>
+        </is>
+      </c>
+      <c r="L110" s="17" t="inlineStr">
+        <is>
+          <t>NOI build, debt service, reversion, unlevered and levered IRR.</t>
+        </is>
+      </c>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>Calendar, horizon &amp; event timing</t>
+        </is>
+      </c>
+      <c r="N110" s="17" t="inlineStr">
+        <is>
+          <t>A floor case: the smallest complete CRE deal, useful as a regression anchor.</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q110" s="17" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>Multifamily development — after-tax</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>Basic Multifamily Development Model (v1.1)</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="inlineStr"/>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H111" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J111" s="17" t="inlineStr">
+        <is>
+          <t>Ground-up multifamily development with an after-tax return</t>
+        </is>
+      </c>
+      <c r="K111" s="17" t="inlineStr">
+        <is>
+          <t>A transit-oriented apartment development held through stabilization and sold.</t>
+        </is>
+      </c>
+      <c r="L111" s="17" t="inlineStr">
+        <is>
+          <t>PGI/vacancy/EGI/opex/RE-tax NOI; capital reserve; debt service; depreciation and amortization add-backs to taxable income; tax at 20%; net-book-value reversion.</t>
+        </is>
+      </c>
+      <c r="M111" s="17" t="inlineStr">
+        <is>
+          <t>Actuarial &amp; tax subsystems (depreciation, tax on taxable income)</t>
+        </is>
+      </c>
+      <c r="N111" s="17" t="inlineStr">
+        <is>
+          <t>The only after-tax CRE convention in the corpus: a second ledger alongside cash.</t>
+        </is>
+      </c>
+      <c r="O111" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P111" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q111" s="17" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>Multifamily — value-add / redevelopment</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>Belasco Multifamily Redevelopment Model</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr"/>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J112" s="17" t="inlineStr">
+        <is>
+          <t>Monthly value-add multifamily redevelopment</t>
+        </is>
+      </c>
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>A unit-by-unit renovation with rents rolling to a post-renovation level.</t>
+        </is>
+      </c>
+      <c r="L112" s="17" t="inlineStr">
+        <is>
+          <t>Unit breakdown driving a monthly pro forma; annual roll-up with returns; amortization schedule.</t>
+        </is>
+      </c>
+      <c r="M112" s="17" t="inlineStr">
+        <is>
+          <t>Cohort / vintage stock (units by renovation status)</t>
+        </is>
+      </c>
+      <c r="N112" s="17" t="inlineStr">
+        <is>
+          <t>Unit-level rollover as a cohort problem rather than a single blended rent.</t>
+        </is>
+      </c>
+      <c r="O112" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P112" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q112" s="17" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>Real estate private equity / JV promote</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>Belasco Equity Waterfall Model</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr"/>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H113" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J113" s="17" t="inlineStr">
+        <is>
+          <t>JV equity waterfall over a redevelopment deal</t>
+        </is>
+      </c>
+      <c r="K113" s="17" t="inlineStr">
+        <is>
+          <t>The Belasco redevelopment distributed through a promote structure.</t>
+        </is>
+      </c>
+      <c r="L113" s="17" t="inlineStr">
+        <is>
+          <t>Tiered waterfall with amortization schedule feeding the underlying model.</t>
+        </is>
+      </c>
+      <c r="M113" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall / priority of payments</t>
+        </is>
+      </c>
+      <c r="N113" s="17" t="inlineStr">
+        <is>
+          <t>A waterfall bound to a real underlying model rather than a synthetic cash flow strip.</t>
+        </is>
+      </c>
+      <c r="O113" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P113" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q113" s="17" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>Real estate debt — construction draw and interest</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>Construction Draw and Interest Calculation Model (v1.31)</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr"/>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H114" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t>S-curve construction draw with capitalized interest</t>
+        </is>
+      </c>
+      <c r="K114" s="17" t="inlineStr">
+        <is>
+          <t>A construction budget drawn on an S-curve, with interest calculated on the running balance.</t>
+        </is>
+      </c>
+      <c r="L114" s="17" t="inlineStr">
+        <is>
+          <t>Sources and uses; budget by cost code; S-curve distribution; interest on average balance.</t>
+        </is>
+      </c>
+      <c r="M114" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state; solve-to-target / endogenous circularity</t>
+        </is>
+      </c>
+      <c r="N114" s="17" t="inlineStr">
+        <is>
+          <t>Capitalized construction interest — the circularity that penzance_highlands builds by hand.</t>
+        </is>
+      </c>
+      <c r="O114" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P114" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q114" s="17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>Real estate development — budget distribution</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>Development Budget Cash Flow Distribution Module</t>
+        </is>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr"/>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H115" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J115" s="17" t="inlineStr">
+        <is>
+          <t>Cost-curve distribution module</t>
+        </is>
+      </c>
+      <c r="K115" s="17" t="inlineStr">
+        <is>
+          <t>A development budget spread over a build period by S-curve.</t>
+        </is>
+      </c>
+      <c r="L115" s="17" t="inlineStr">
+        <is>
+          <t>Budget by line item; S-curve weights; period distribution.</t>
+        </is>
+      </c>
+      <c r="M115" s="17" t="inlineStr">
+        <is>
+          <t>Curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N115" s="17" t="inlineStr">
+        <is>
+          <t>Curve lowering in isolation — a unit test for the cost-curve mechanism.</t>
+        </is>
+      </c>
+      <c r="O115" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P115" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q115" s="17" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — acquisition</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Acquisition Model (v1.3)</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr"/>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J116" s="17" t="inlineStr">
+        <is>
+          <t>Institutional acquisition DCF with investor returns</t>
+        </is>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
+        <is>
+          <t>A stabilized asset acquired, held and sold, with a separate investor-return layer.</t>
+        </is>
+      </c>
+      <c r="L116" s="17" t="inlineStr">
+        <is>
+          <t>Property summary, operating-statement DCF, debt module, property vs investor returns.</t>
+        </is>
+      </c>
+      <c r="M116" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N116" s="17" t="inlineStr">
+        <is>
+          <t>The property/investor return split — two return layers over one cash flow.</t>
+        </is>
+      </c>
+      <c r="O116" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P116" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q116" s="17" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — acquisition</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Acquisition Model — operating, investment and return</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr"/>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H117" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J117" s="17" t="inlineStr">
+        <is>
+          <t>Acquisition model with an amortization schedule</t>
+        </is>
+      </c>
+      <c r="K117" s="17" t="inlineStr">
+        <is>
+          <t>A held-and-sold asset with an explicit loan schedule.</t>
+        </is>
+      </c>
+      <c r="L117" s="17" t="inlineStr">
+        <is>
+          <t>Single-sheet model plus amortization schedule.</t>
+        </is>
+      </c>
+      <c r="M117" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state</t>
+        </is>
+      </c>
+      <c r="N117" s="17" t="inlineStr">
+        <is>
+          <t>A second independent implementation of the acquisition conventions in ID 115.</t>
+        </is>
+      </c>
+      <c r="O117" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P117" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q117" s="17" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — portfolio</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Portfolio Acquisition Model (v2.3)</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J118" s="17" t="inlineStr">
+        <is>
+          <t>Multi-property portfolio acquisition</t>
+        </is>
+      </c>
+      <c r="K118" s="17" t="inlineStr">
+        <is>
+          <t>Several assets underwritten separately and rolled to a portfolio.</t>
+        </is>
+      </c>
+      <c r="L118" s="17" t="inlineStr">
+        <is>
+          <t>Per-property assumptions and returns; portfolio-level roll-up; investor-level returns; debt.</t>
+        </is>
+      </c>
+      <c r="M118" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N118" s="17" t="inlineStr">
+        <is>
+          <t>Three return layers (property, portfolio, investor) — nothing in the suite covers a portfolio roll-up.</t>
+        </is>
+      </c>
+      <c r="O118" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P118" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q118" s="17" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>Real estate private equity / JV promote</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Equity Waterfall — combined (v1.122)</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr"/>
+      <c r="G119" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H119" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J119" s="17" t="inlineStr">
+        <is>
+          <t>Equity waterfall, combined annual/monthly</t>
+        </is>
+      </c>
+      <c r="K119" s="17" t="inlineStr">
+        <is>
+          <t>An investor-return waterfall on a single sheet.</t>
+        </is>
+      </c>
+      <c r="L119" s="17" t="inlineStr">
+        <is>
+          <t>Tiered distribution with catch-up.</t>
+        </is>
+      </c>
+      <c r="M119" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall / priority of payments</t>
+        </is>
+      </c>
+      <c r="N119" s="17" t="inlineStr">
+        <is>
+          <t>Waterfall tier arithmetic isolated from an underlying property model.</t>
+        </is>
+      </c>
+      <c r="O119" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P119" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q119" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>Real estate private equity / JV promote</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Equity Waterfall — monthly (v1.1)</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr"/>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
+        <is>
+          <t>Monthly equity waterfall</t>
+        </is>
+      </c>
+      <c r="K120" s="17" t="inlineStr">
+        <is>
+          <t>The same structure as ID 118 on a monthly period.</t>
+        </is>
+      </c>
+      <c r="L120" s="17" t="inlineStr">
+        <is>
+          <t>Monthly tier accrual and distribution.</t>
+        </is>
+      </c>
+      <c r="M120" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; calendar, horizon &amp; event timing</t>
+        </is>
+      </c>
+      <c r="N120" s="17" t="inlineStr">
+        <is>
+          <t>Whether a promote computed monthly and annually agree — a period-convention check.</t>
+        </is>
+      </c>
+      <c r="O120" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P120" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q120" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>Multifamily / apartment acquisition — stochastic</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>Apartment Acquisition Model with Monte Carlo (v2.1)</t>
+        </is>
+      </c>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr"/>
+      <c r="G121" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H121" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J121" s="17" t="inlineStr">
+        <is>
+          <t>Monthly multifamily acquisition with a Monte Carlo layer</t>
+        </is>
+      </c>
+      <c r="K121" s="17" t="inlineStr">
+        <is>
+          <t>A rent-roll-driven apartment acquisition with stochastic rent, vacancy and exit assumptions.</t>
+        </is>
+      </c>
+      <c r="L121" s="17" t="inlineStr">
+        <is>
+          <t>MF rent roll; rents, capex, rollover, free rent, vacancy and releasing as separate monthly modules; 10,000-trial Monte Carlo sheet; property and investor returns.</t>
+        </is>
+      </c>
+      <c r="M121" s="17" t="inlineStr">
+        <is>
+          <t>Stochastic drivers &amp; event Monte Carlo; cohort / vintage stock</t>
+        </is>
+      </c>
+      <c r="N121" s="17" t="inlineStr">
+        <is>
+          <t>The only Monte Carlo reference in the CRE corpus — an aggregate-distribution assertion target.</t>
+        </is>
+      </c>
+      <c r="O121" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P121" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q121" s="17" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>Single-family residential investment</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>Single-Family Residential Investment Model (v1.12)</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr"/>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H122" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J122" s="17" t="inlineStr">
+        <is>
+          <t>Single-family buy/renovate/hold</t>
+        </is>
+      </c>
+      <c r="K122" s="17" t="inlineStr">
+        <is>
+          <t>A single house acquired, renovated on a construction budget and held.</t>
+        </is>
+      </c>
+      <c r="L122" s="17" t="inlineStr">
+        <is>
+          <t>Construction budget; proforma; monthly cash flow; summary returns.</t>
+        </is>
+      </c>
+      <c r="M122" s="17" t="inlineStr">
+        <is>
+          <t>Calendar, horizon &amp; event timing</t>
+        </is>
+      </c>
+      <c r="N122" s="17" t="inlineStr">
+        <is>
+          <t>Small-asset conventions — no rent roll, no tenant rollover.</t>
+        </is>
+      </c>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P122" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q122" s="17" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — modeling technique</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>OFFSET in Real Estate Modeling</t>
+        </is>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr"/>
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H123" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J123" s="17" t="inlineStr">
+        <is>
+          <t>Technique demonstration</t>
+        </is>
+      </c>
+      <c r="K123" s="17" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month calculations built with an OFFSET window.</t>
+        </is>
+      </c>
+      <c r="L123" s="17" t="inlineStr">
+        <is>
+          <t>Rolling-window aggregation over a period series.</t>
+        </is>
+      </c>
+      <c r="M123" s="17" t="inlineStr">
+        <is>
+          <t>Curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N123" s="17" t="inlineStr">
+        <is>
+          <t>Rolling-window aggregation (TTM), which the language expresses with series_sum over a bounded range.</t>
+        </is>
+      </c>
+      <c r="O123" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P123" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q123" s="17" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>Hotels / hospitality</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>Hotel Acquisition Model (USALI departmental)</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr"/>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H124" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
+        <is>
+          <t>10-year hotel acquisition, full USALI departmental structure</t>
+        </is>
+      </c>
+      <c r="K124" s="17" t="inlineStr">
+        <is>
+          <t>A 175-key full-service hotel acquired Oct 2018, 60% LTV with a 2-year IO period then 30-year amortization, sold at a 7% exit cap.</t>
+        </is>
+      </c>
+      <c r="L124" s="17" t="inlineStr">
+        <is>
+          <t>Occupancy/ADR/RevPAR penetration indices; rooms, F&amp;B and other operating departments each with revenue, expense and departmental profit; undistributed expenses; franchise and management fees; fixed expenses; NOI; FF&amp;E reserve; unlevered and levered returns.</t>
+        </is>
+      </c>
+      <c r="M124" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N124" s="17" t="inlineStr">
+        <is>
+          <t>Departmental hotel P&amp;L — no CRE case has revenue built from a rate x volume index.</t>
+        </is>
+      </c>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P124" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q124" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>Hotels / hospitality — value-add</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>Value-Add Hotel Valuation Model</t>
+        </is>
+      </c>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr"/>
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H125" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J125" s="17" t="inlineStr">
+        <is>
+          <t>5-year value-add hotel valuation, unlevered and levered</t>
+        </is>
+      </c>
+      <c r="K125" s="17" t="inlineStr">
+        <is>
+          <t>A hotel bought, repositioned with a $6M capital improvement in year 1, and sold.</t>
+        </is>
+      </c>
+      <c r="L125" s="17" t="inlineStr">
+        <is>
+          <t>NOI build from a P&amp;L; PV of cash flow vs PV of resale; terminal value and selling costs; unlevered IRR partitioned into income and residual; branding scenario switch.</t>
+        </is>
+      </c>
+      <c r="M125" s="17" t="inlineStr">
+        <is>
+          <t>Calendar, horizon &amp; event timing; piecewise, threshold &amp; greater-of expressions</t>
+        </is>
+      </c>
+      <c r="N125" s="17" t="inlineStr">
+        <is>
+          <t>Unlevered throughout, so model.npv is assertable — no existing CRE case asserts it.</t>
+        </is>
+      </c>
+      <c r="O125" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P125" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q125" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>Public subsidy — tax increment financing</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>Tax Increment Financing (TIF) Sample Analysis</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>PropertyMetrics</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr"/>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t>TIF-supported redevelopment, run with and without the subsidy</t>
+        </is>
+      </c>
+      <c r="K126" s="17" t="inlineStr">
+        <is>
+          <t>A $10M property redeveloped for $7.5M, with the increment captured across three tax bases.</t>
+        </is>
+      </c>
+      <c r="L126" s="17" t="inlineStr">
+        <is>
+          <t>Real property, retail sales and personal property increments, each with its own assessment ratio, capture percentage and inflation/depreciation factor, against a five-district levy table with separate TIF columns; feasibility run twice — IRR 7.139% without TIF, 13.51% with.</t>
+        </is>
+      </c>
+      <c r="M126" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity; curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N126" s="17" t="inlineStr">
+        <is>
+          <t>A paired with/without comparison — a stronger assertion shape than a single IRR, and the only public-subsidy revenue stream in the corpus.</t>
+        </is>
+      </c>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P126" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q126" s="17" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>Multi-asset commercial real estate</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>A.CRE All-in-One (Ai1) Underwriting Model</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>Adventures in CRE (A.CRE)</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr"/>
+      <c r="G127" s="17" t="inlineStr">
+        <is>
+          <t>free registration</t>
+        </is>
+      </c>
+      <c r="H127" s="17" t="inlineStr">
+        <is>
+          <t>"Pay What You're Able" — not cleared for redistribution</t>
+        </is>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J127" s="17" t="inlineStr">
+        <is>
+          <t>Monthly institutional underwriting across property types</t>
+        </is>
+      </c>
+      <c r="K127" s="17" t="inlineStr">
+        <is>
+          <t>A.CRE's flagship general-purpose underwriting model.</t>
+        </is>
+      </c>
+      <c r="L127" s="17" t="inlineStr">
+        <is>
+          <t>Lease-by-lease rent roll, development and acquisition modes, debt and waterfall modules.</t>
+        </is>
+      </c>
+      <c r="M127" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N127" s="17" t="inlineStr">
+        <is>
+          <t>Already catalogued as ID 1; this is the local copy. Not read: .xlsb needs pyxlsb.</t>
+        </is>
+      </c>
+      <c r="O127" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P127" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q127" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>Affordable housing — homeownership / PHA</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>Homeownership development budget with PHA mortgage analysis</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr"/>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H128" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
+        <is>
+          <t>Affordable for-sale housing development budget</t>
+        </is>
+      </c>
+      <c r="K128" s="17" t="inlineStr">
+        <is>
+          <t>A homeownership development with construction and permanent financing and a sales schedule.</t>
+        </is>
+      </c>
+      <c r="L128" s="17" t="inlineStr">
+        <is>
+          <t>Construction and permanent financing sheets; unit mix; sales financing schedule; public housing authority mortgage analysis.</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="inlineStr">
+        <is>
+          <t>For-sale affordable housing with a subsidized mortgage — adjacent to hud_home_multifamily.</t>
+        </is>
+      </c>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P128" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q128" s="17" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>Mixed-use development — master plan</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>Mixed-use master plan financial model with infrastructure allocation</t>
+        </is>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr"/>
+      <c r="G129" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H129" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J129" s="17" t="inlineStr">
+        <is>
+          <t>Master-planned mixed-use development</t>
+        </is>
+      </c>
+      <c r="K129" s="17" t="inlineStr">
+        <is>
+          <t>A multi-parcel master plan with rental, for-sale, office, retail, hotel and structured parking.</t>
+        </is>
+      </c>
+      <c r="L129" s="17" t="inlineStr">
+        <is>
+          <t>Development program; infrastructure costs distributed across land uses; a separate pro forma per product type.</t>
+        </is>
+      </c>
+      <c r="M129" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N129" s="17" t="inlineStr">
+        <is>
+          <t>Shared-cost allocation across product types — the podium problem in penzance_highlands, generalized.</t>
+        </is>
+      </c>
+      <c r="O129" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P129" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q129" s="17" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>Energy &amp; Infrastructure (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>Infrastructure — parking concession pricing</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>Car parking pricing model</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr"/>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t>Parking facility pricing and cost recovery</t>
+        </is>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>A car park priced to recover costs over a concession term.</t>
+        </is>
+      </c>
+      <c r="L130" s="17" t="inlineStr">
+        <is>
+          <t>Input data, cost build, revenue build, combined cost and revenue comparison.</t>
+        </is>
+      </c>
+      <c r="M130" s="17" t="inlineStr">
+        <is>
+          <t>Curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N130" s="17" t="inlineStr">
+        <is>
+          <t>A small infrastructure concession — the simplest form of the PPP structures in IDs 29-34.</t>
+        </is>
+      </c>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P130" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q130" s="17" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>Hotels / hospitality</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — full-service hotel operating reforecast</t>
+        </is>
+      </c>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr"/>
+      <c r="G131" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H131" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J131" s="17" t="inlineStr">
+        <is>
+          <t>Mid-year operating reforecast for a full-service hotel</t>
+        </is>
+      </c>
+      <c r="K131" s="17" t="inlineStr">
+        <is>
+          <t>A single hotel's departmental financials reforecast against budget.</t>
+        </is>
+      </c>
+      <c r="L131" s="17" t="inlineStr">
+        <is>
+          <t>One-sheet departmental operating statement, actual-to-date plus forecast.</t>
+        </is>
+      </c>
+      <c r="M131" s="17" t="inlineStr">
+        <is>
+          <t>Calendar, horizon &amp; event timing</t>
+        </is>
+      </c>
+      <c r="N131" s="17" t="inlineStr">
+        <is>
+          <t>Realized-versus-forecast operating data — the axis docs/20 §2.2 records as uncovered.</t>
+        </is>
+      </c>
+      <c r="O131" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P131" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q131" s="17" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>Mixed-use resort — hotel, condo, retail</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — waterfront mixed-use resort JV</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr"/>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H132" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t>Investor model for a mixed-use resort development</t>
+        </is>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
+        <is>
+          <t>A waterfront development combining luxury hotel, private residences and retail under a JV.</t>
+        </is>
+      </c>
+      <c r="L132" s="17" t="inlineStr">
+        <is>
+          <t>Sources and uses; budget summary; equity assumptions and returns; project and sponsor waterfalls run separately; terminal sale summary; retail rent roll; per-component cash flows.</t>
+        </is>
+      </c>
+      <c r="M132" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N132" s="17" t="inlineStr">
+        <is>
+          <t>Two waterfalls over one deal (project and sponsor) — a nesting the suite does not cover.</t>
+        </is>
+      </c>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P132" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q132" s="17" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>Condominium development — urban infill</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — urban condominium redevelopment</t>
+        </is>
+      </c>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr"/>
+      <c r="G133" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H133" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J133" s="17" t="inlineStr">
+        <is>
+          <t>Condominium redevelopment with a unit-closing schedule</t>
+        </is>
+      </c>
+      <c r="K133" s="17" t="inlineStr">
+        <is>
+          <t>An infill condominium redesign sold unit by unit.</t>
+        </is>
+      </c>
+      <c r="L133" s="17" t="inlineStr">
+        <is>
+          <t>Stacking plan; unit closings; soft costs and budget detail; monthly and annual condo cash flows; investor waterfall; working-capital loan interest; sensitivity grid.</t>
+        </is>
+      </c>
+      <c r="M133" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state; ordered waterfall</t>
+        </is>
+      </c>
+      <c r="N133" s="17" t="inlineStr">
+        <is>
+          <t>A stacking plan driving closings — condominium sellout at unit granularity.</t>
+        </is>
+      </c>
+      <c r="O133" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P133" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q133" s="17" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>Seniors housing / apartment development</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>Private investment-committee template — seniors housing development</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr"/>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
+        <is>
+          <t>Investment-committee development template</t>
+        </is>
+      </c>
+      <c r="K134" s="17" t="inlineStr">
+        <is>
+          <t>A ground-up seniors housing / apartment development presented for IC approval.</t>
+        </is>
+      </c>
+      <c r="L134" s="17" t="inlineStr">
+        <is>
+          <t>Summary inputs; development budget with an exhibit; leveraged and unleveraged annual summaries; operating statement; permanent loan schedule; partner pro forma.</t>
+        </is>
+      </c>
+      <c r="M134" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N134" s="17" t="inlineStr">
+        <is>
+          <t>Leveraged and unleveraged views of one deal held side by side — a consistency check.</t>
+        </is>
+      </c>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P134" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q134" s="17" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>Single-family land development — phased</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — phased single-family land development</t>
+        </is>
+      </c>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr"/>
+      <c r="G135" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H135" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J135" s="17" t="inlineStr">
+        <is>
+          <t>Phased residential land development with a revolving credit line</t>
+        </is>
+      </c>
+      <c r="K135" s="17" t="inlineStr">
+        <is>
+          <t>A single-family subdivision built in a horizontal phase plus two vertical phases.</t>
+        </is>
+      </c>
+      <c r="L135" s="17" t="inlineStr">
+        <is>
+          <t>Bell-curve cost distribution; revolving line of credit analysis; down-payment scenarios; cost sheet; per-phase budgets and cash flows.</t>
+        </is>
+      </c>
+      <c r="M135" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state; curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N135" s="17" t="inlineStr">
+        <is>
+          <t>A revolver — a facility that draws and repays repeatedly, unlike the one-way construction facilities the suite covers.</t>
+        </is>
+      </c>
+      <c r="O135" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P135" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q135" s="17" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>Mixed-income residential — ground lease</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — mixed-income residential development on a ground lease</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr"/>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
+        <is>
+          <t>Mixed-income residential development held 60 years</t>
+        </is>
+      </c>
+      <c r="K136" s="17" t="inlineStr">
+        <is>
+          <t>A large mixed-income residential development on leased land, with AMI-restricted rents.</t>
+        </is>
+      </c>
+      <c r="L136" s="17" t="inlineStr">
+        <is>
+          <t>Project budget; unit mix; AMI rent tiers; monthly and annual operating cash flows; construction cash flows; ground lease; tax worksheet; 60-year pro forma; refinancing.</t>
+        </is>
+      </c>
+      <c r="M136" s="17" t="inlineStr">
+        <is>
+          <t>Calendar, horizon &amp; event timing; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N136" s="17" t="inlineStr">
+        <is>
+          <t>A 60-year horizon with a refinancing mid-life, and income-restricted rent tiers.</t>
+        </is>
+      </c>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P136" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q136" s="17" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>Hotel and condominium development — JV</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — hotel and condominium development JV</t>
+        </is>
+      </c>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr"/>
+      <c r="G137" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H137" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J137" s="17" t="inlineStr">
+        <is>
+          <t>Combined hotel and for-sale condominium development</t>
+        </is>
+      </c>
+      <c r="K137" s="17" t="inlineStr">
+        <is>
+          <t>A resort development carrying a hotel and a condominium on one construction basis.</t>
+        </is>
+      </c>
+      <c r="L137" s="17" t="inlineStr">
+        <is>
+          <t>Development program split public-area and F&amp;B; detailed budget and funding; equity contribution; hotel cost spread and operations; quarterly and annual rollups; pre-sale economics; condo sales and trading program; combined waterfall and returns summary.</t>
+        </is>
+      </c>
+      <c r="M137" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N137" s="17" t="inlineStr">
+        <is>
+          <t>Hotel and condominium on one basis with quarterly and annual rollups of the same cash flow.</t>
+        </is>
+      </c>
+      <c r="O137" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P137" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q137" s="17" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>Real estate fund — GP/LP</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>Private fund model — GP/LP waterfall over a property portfolio</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr"/>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J138" s="17" t="inlineStr">
+        <is>
+          <t>Fund-level waterfall over multiple properties</t>
+        </is>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
+        <is>
+          <t>A real estate fund with numbered property models rolling into fund-level distributions.</t>
+        </is>
+      </c>
+      <c r="L138" s="17" t="inlineStr">
+        <is>
+          <t>Fund tear sheet; fund and property inputs; property summary; separate property and development waterfalls; a GP waterfall and a 'super GP as developer' layer.</t>
+        </is>
+      </c>
+      <c r="M138" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N138" s="17" t="inlineStr">
+        <is>
+          <t>Three stacked waterfalls (property, development, GP) — the deepest nesting in the corpus.</t>
+        </is>
+      </c>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P138" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q138" s="17" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>Condominium — co-investment</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — condominium co-investment</t>
+        </is>
+      </c>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr"/>
+      <c r="G139" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H139" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J139" s="17" t="inlineStr">
+        <is>
+          <t>Condominium development held through a co-investment vehicle</t>
+        </is>
+      </c>
+      <c r="K139" s="17" t="inlineStr">
+        <is>
+          <t>A condominium project underwritten for a co-investor.</t>
+        </is>
+      </c>
+      <c r="L139" s="17" t="inlineStr">
+        <is>
+          <t>Underwriting summary; budget; cash flow; waterfall; Gantt chart; maintenance summary.</t>
+        </is>
+      </c>
+      <c r="M139" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; calendar, horizon &amp; event timing</t>
+        </is>
+      </c>
+      <c r="N139" s="17" t="inlineStr">
+        <is>
+          <t>A schedule (Gantt) driving the cash flow rather than a fixed period offset.</t>
+        </is>
+      </c>
+      <c r="O139" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P139" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q139" s="17" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>Condominium — template</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Private template — condominium development with partner cash flow</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr"/>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>Reusable condominium underwriting template</t>
+        </is>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
+        <is>
+          <t>A condominium template with revenue inputs, partner splits and scenario summaries.</t>
+        </is>
+      </c>
+      <c r="L140" s="17" t="inlineStr">
+        <is>
+          <t>Revenue inputs; cash flow; partner cash flow; PIR tables; sensitivity and scenario summary.</t>
+        </is>
+      </c>
+      <c r="M140" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N140" s="17" t="inlineStr">
+        <is>
+          <t>A partner-level cash flow derived from a project-level one — the same split as ID 115.</t>
+        </is>
+      </c>
+      <c r="O140" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P140" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q140" s="17" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>Multifamily development — mezzanine</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — multifamily development with mezzanine notes</t>
+        </is>
+      </c>
+      <c r="E141" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr"/>
+      <c r="G141" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H141" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J141" s="17" t="inlineStr">
+        <is>
+          <t>265-unit multifamily development with a note structure</t>
+        </is>
+      </c>
+      <c r="K141" s="17" t="inlineStr">
+        <is>
+          <t>A ground-up apartment development financed with senior and mezzanine notes.</t>
+        </is>
+      </c>
+      <c r="L141" s="17" t="inlineStr">
+        <is>
+          <t>Global and capital inputs; notes calculation; residual value; cash flow; equity waterfall.</t>
+        </is>
+      </c>
+      <c r="M141" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; per-period persistent state</t>
+        </is>
+      </c>
+      <c r="N141" s="17" t="inlineStr">
+        <is>
+          <t>A mezzanine tranche between senior debt and equity — a layer the suite does not model.</t>
+        </is>
+      </c>
+      <c r="O141" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P141" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q141" s="17" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>Structured real estate debt — mezzanine sizing</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — structured debt and mezzanine sizing review</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr"/>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>Lender-side review of a structured debt request</t>
+        </is>
+      </c>
+      <c r="K142" s="17" t="inlineStr">
+        <is>
+          <t>A development loan request reviewed by a capital provider, sized under several cases.</t>
+        </is>
+      </c>
+      <c r="L142" s="17" t="inlineStr">
+        <is>
+          <t>Loan request; stabilized operations; detailed project costs; cash flow and return summary; structured debt output; mezzanine-only output; takeover underwriting; case assumptions.</t>
+        </is>
+      </c>
+      <c r="M142" s="17" t="inlineStr">
+        <is>
+          <t>Trigger, covenant &amp; regime switch; piecewise, threshold &amp; greater-of expressions</t>
+        </is>
+      </c>
+      <c r="N142" s="17" t="inlineStr">
+        <is>
+          <t>Debt sized to a constraint rather than stated — solve-to-target on a coverage test.</t>
+        </is>
+      </c>
+      <c r="O142" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P142" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q142" s="17" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="17" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>Private equity fund — pacing and gross-to-net</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>Private fund model — commitment pacing, capital calls and gross-to-net</t>
+        </is>
+      </c>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr"/>
+      <c r="G143" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H143" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J143" s="17" t="inlineStr">
+        <is>
+          <t>Fund-level pro forma with capital call pacing</t>
+        </is>
+      </c>
+      <c r="K143" s="17" t="inlineStr">
+        <is>
+          <t>A closed-end fund modeled from commitments through gross and net returns.</t>
+        </is>
+      </c>
+      <c r="L143" s="17" t="inlineStr">
+        <is>
+          <t>Fund assumptions; deal summary; annual and calendar fund-level summaries; gross-to-net bridge; GP summary; LP and subscription-line terms; expense inputs; capital call inputs; pacing assumptions; tax-only view.</t>
+        </is>
+      </c>
+      <c r="M143" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; solve-to-target / endogenous circularity</t>
+        </is>
+      </c>
+      <c r="N143" s="17" t="inlineStr">
+        <is>
+          <t>A subscription line and a gross-to-net bridge — the fund mechanics behind catalogue IDs 79-80.</t>
+        </is>
+      </c>
+      <c r="O143" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P143" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q143" s="17" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>Retail — JV development</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — retail JV with a two-tier waterfall</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr"/>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J144" s="17" t="inlineStr">
+        <is>
+          <t>Retail development held in a JV, with ARGUS output as the rent source</t>
+        </is>
+      </c>
+      <c r="K144" s="17" t="inlineStr">
+        <is>
+          <t>A retail parcel developed and held, with the rent roll imported from ARGUS.</t>
+        </is>
+      </c>
+      <c r="L144" s="17" t="inlineStr">
+        <is>
+          <t>Monthly and annual cash flows; JV partnership structure; two separate waterfalls; senior and permanent loan amortization; ARGUS output sheet.</t>
+        </is>
+      </c>
+      <c r="M144" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N144" s="17" t="inlineStr">
+        <is>
+          <t>Construction-to-permanent refinancing, and a rent roll sourced from valuation software.</t>
+        </is>
+      </c>
+      <c r="O144" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P144" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q144" s="17" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
+        <is>
+          <t>Preferred equity</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — preferred equity with a draw schedule</t>
+        </is>
+      </c>
+      <c r="E145" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr"/>
+      <c r="G145" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H145" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J145" s="17" t="inlineStr">
+        <is>
+          <t>Preferred equity position with disbursement and waterfall checks</t>
+        </is>
+      </c>
+      <c r="K145" s="17" t="inlineStr">
+        <is>
+          <t>A preferred equity investment funded on a draw schedule against a development budget.</t>
+        </is>
+      </c>
+      <c r="L145" s="17" t="inlineStr">
+        <is>
+          <t>Budget; disbursement schedule; draw requests; year-2 and year-3 waterfalls; a waterfall check sheet; a discrepancy sheet; hidden cash-flow/IRR sheet; co-GP economics.</t>
+        </is>
+      </c>
+      <c r="M145" s="17" t="inlineStr">
+        <is>
+          <t>Ordered waterfall; per-period persistent state</t>
+        </is>
+      </c>
+      <c r="N145" s="17" t="inlineStr">
+        <is>
+          <t>Preferred equity accrual and catch-up — a position type the suite does not cover, with the workbook's own check sheet as a second reference.</t>
+        </is>
+      </c>
+      <c r="O145" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P145" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q145" s="17" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>Hotels / hospitality — development</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — hotel development with a USALI pro forma</t>
+        </is>
+      </c>
+      <c r="E146" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr"/>
+      <c r="G146" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H146" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J146" s="17" t="inlineStr">
+        <is>
+          <t>Ground-up hotel development held through stabilization</t>
+        </is>
+      </c>
+      <c r="K146" s="17" t="inlineStr">
+        <is>
+          <t>A hotel developed, opened and operated on a USALI departmental structure.</t>
+        </is>
+      </c>
+      <c r="L146" s="17" t="inlineStr">
+        <is>
+          <t>Inputs and working sheets; waterfall; USALI operating pro forma; development pro forma.</t>
+        </is>
+      </c>
+      <c r="M146" s="17" t="inlineStr">
+        <is>
+          <t>Per-period persistent state; ordered waterfall</t>
+        </is>
+      </c>
+      <c r="N146" s="17" t="inlineStr">
+        <is>
+          <t>Development and operations on one basis, with the ramp from opening to stabilization.</t>
+        </is>
+      </c>
+      <c r="O146" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P146" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q146" s="17" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>Hotels / hospitality — repositioning</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — hotel repositioning ROI with STR benchmarking</t>
+        </is>
+      </c>
+      <c r="E147" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr"/>
+      <c r="G147" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H147" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J147" s="17" t="inlineStr">
+        <is>
+          <t>Return on a hotel repositioning investment</t>
+        </is>
+      </c>
+      <c r="K147" s="17" t="inlineStr">
+        <is>
+          <t>A hotel repositioned against its competitive set, benchmarked on STR data.</t>
+        </is>
+      </c>
+      <c r="L147" s="17" t="inlineStr">
+        <is>
+          <t>Competitive set comparison; operating history; detailed F&amp;B analysis; pro forma versus comparables; ROI analysis; STR raw data and STAR/TREND responses; refinancing reference.</t>
+        </is>
+      </c>
+      <c r="M147" s="17" t="inlineStr">
+        <is>
+          <t>Curves, indices &amp; price paths</t>
+        </is>
+      </c>
+      <c r="N147" s="17" t="inlineStr">
+        <is>
+          <t>Penetration indices against a measured competitive set rather than assumed — the empirical version of the Hotel Acquisition Model's penetration sheet.</t>
+        </is>
+      </c>
+      <c r="O147" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P147" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q147" s="17" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>Commercial real estate — unclassified</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — not yet read (.xlsb)</t>
+        </is>
+      </c>
+      <c r="E148" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr"/>
+      <c r="G148" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H148" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J148" s="17" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="K148" s="17" t="inlineStr">
+        <is>
+          <t>Not established — the file was not opened.</t>
+        </is>
+      </c>
+      <c r="L148" s="17" t="inlineStr">
+        <is>
+          <t>Not established.</t>
+        </is>
+      </c>
+      <c r="M148" s="17" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="N148" s="17" t="inlineStr">
+        <is>
+          <t>Requires pyxlsb to read; classify before use.</t>
+        </is>
+      </c>
+      <c r="O148" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P148" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q148" s="17" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>CRE (existing pack)</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>Residential development — international</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>Private deal model — international residential developer (not yet read, .xlsb)</t>
+        </is>
+      </c>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>Private (client corpus)</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr"/>
+      <c r="G149" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H149" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J149" s="17" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="K149" s="17" t="inlineStr">
+        <is>
+          <t>Not established — the file was not opened.</t>
+        </is>
+      </c>
+      <c r="L149" s="17" t="inlineStr">
+        <is>
+          <t>Not established.</t>
+        </is>
+      </c>
+      <c r="M149" s="17" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="N149" s="17" t="inlineStr">
+        <is>
+          <t>Requires pyxlsb to read; classify before use.</t>
+        </is>
+      </c>
+      <c r="O149" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P149" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q149" s="17" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>Consumer foods — M&amp;A</t>
+        </is>
+      </c>
+      <c r="D150" s="17" t="inlineStr">
+        <is>
+          <t>Kraft / Kellogg accretion-dilution exercise (worked solution)</t>
+        </is>
+      </c>
+      <c r="E150" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr"/>
+      <c r="G150" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H150" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J150" s="17" t="inlineStr">
+        <is>
+          <t>Merger accretion/dilution analysis</t>
+        </is>
+      </c>
+      <c r="K150" s="17" t="inlineStr">
+        <is>
+          <t>A hypothetical acquisition of one listed food company by another.</t>
+        </is>
+      </c>
+      <c r="L150" s="17" t="inlineStr">
+        <is>
+          <t>Pro forma EPS accretion/dilution across consideration mixes.</t>
+        </is>
+      </c>
+      <c r="M150" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N150" s="17" t="inlineStr">
+        <is>
+          <t>Per-share accretion — a metric defined on a combined entity, not on cash flows.</t>
+        </is>
+      </c>
+      <c r="O150" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P150" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q150" s="17" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>Consumer foods — M&amp;A</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>Kraft / Kellogg full merger model (worked solution)</t>
+        </is>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr"/>
+      <c r="G151" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H151" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J151" s="17" t="inlineStr">
+        <is>
+          <t>Full merger model with synergies</t>
+        </is>
+      </c>
+      <c r="K151" s="17" t="inlineStr">
+        <is>
+          <t>The same combination as ID 149, modeled end to end.</t>
+        </is>
+      </c>
+      <c r="L151" s="17" t="inlineStr">
+        <is>
+          <t>Merger assumptions; pro forma balance sheet; operating model; synergies model; sensitivities.</t>
+        </is>
+      </c>
+      <c r="M151" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N151" s="17" t="inlineStr">
+        <is>
+          <t>A synergy schedule phased in over time — a stream that exists only post-combination.</t>
+        </is>
+      </c>
+      <c r="O151" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P151" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q151" s="17" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>Consumer foods — comparable analysis</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
+        <is>
+          <t>Heinz comparable-company financial spread (worked solution)</t>
+        </is>
+      </c>
+      <c r="E152" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F152" s="17" t="inlineStr"/>
+      <c r="G152" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H152" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J152" s="17" t="inlineStr">
+        <is>
+          <t>Comparable company spread</t>
+        </is>
+      </c>
+      <c r="K152" s="17" t="inlineStr">
+        <is>
+          <t>One company's financials normalized for comparison.</t>
+        </is>
+      </c>
+      <c r="L152" s="17" t="inlineStr">
+        <is>
+          <t>Normalization adjustments and multiple calculation.</t>
+        </is>
+      </c>
+      <c r="M152" s="17" t="inlineStr">
+        <is>
+          <t>Other / uncategorised</t>
+        </is>
+      </c>
+      <c r="N152" s="17" t="inlineStr">
+        <is>
+          <t>Multiple-based valuation, which CFDL does not express as cash flows — a scope boundary.</t>
+        </is>
+      </c>
+      <c r="O152" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P152" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q152" s="17" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>Cross-industry — sponsor buyout</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>LBO model (worked solution)</t>
+        </is>
+      </c>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="inlineStr"/>
+      <c r="G153" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H153" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J153" s="17" t="inlineStr">
+        <is>
+          <t>Sponsor buyout with a debt schedule</t>
+        </is>
+      </c>
+      <c r="K153" s="17" t="inlineStr">
+        <is>
+          <t>A generic leveraged buyout held and exited.</t>
+        </is>
+      </c>
+      <c r="L153" s="17" t="inlineStr">
+        <is>
+          <t>Sources and uses; pro forma balance sheet; operating model with a debt schedule.</t>
+        </is>
+      </c>
+      <c r="M153" s="17" t="inlineStr">
+        <is>
+          <t>Solve-to-target / endogenous circularity</t>
+        </is>
+      </c>
+      <c r="N153" s="17" t="inlineStr">
+        <is>
+          <t>A second independent reference for the conventions in benchmarks/opco/lbo_buyout.</t>
+        </is>
+      </c>
+      <c r="O153" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P153" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q153" s="17" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>Real estate operating company — buyout</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>LBO of a property operating company, with NOI and FFO</t>
+        </is>
+      </c>
+      <c r="E154" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F154" s="17" t="inlineStr"/>
+      <c r="G154" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H154" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I154" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J154" s="17" t="inlineStr">
+        <is>
+          <t>Buyout of a real-estate operating company</t>
+        </is>
+      </c>
+      <c r="K154" s="17" t="inlineStr">
+        <is>
+          <t>An LBO where the operating cash flow is property NOI and the metric is FFO.</t>
+        </is>
+      </c>
+      <c r="L154" s="17" t="inlineStr">
+        <is>
+          <t>NOI assumptions; levered and unlevered returns on a cap-rate exit; ratios; DCF; FFO projection.</t>
+        </is>
+      </c>
+      <c r="M154" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N154" s="17" t="inlineStr">
+        <is>
+          <t>The CRE/OpCo boundary — a buyout whose EBITDA is NOI and whose exit is a cap rate.</t>
+        </is>
+      </c>
+      <c r="O154" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P154" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q154" s="17" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>Cross-industry — sponsor buyout</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>Sovereign fund LBO template with a DCF cross-check</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr"/>
+      <c r="G155" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H155" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J155" s="17" t="inlineStr">
+        <is>
+          <t>Buyout template with a parallel DCF</t>
+        </is>
+      </c>
+      <c r="K155" s="17" t="inlineStr">
+        <is>
+          <t>A buyout modeled alongside an intrinsic valuation of the same business.</t>
+        </is>
+      </c>
+      <c r="L155" s="17" t="inlineStr">
+        <is>
+          <t>Assumptions; financial statements; LBO and LBO output; DCF; hedge-fund view; calculations.</t>
+        </is>
+      </c>
+      <c r="M155" s="17" t="inlineStr">
+        <is>
+          <t>Solve-to-target / endogenous circularity</t>
+        </is>
+      </c>
+      <c r="N155" s="17" t="inlineStr">
+        <is>
+          <t>An LBO return and a DCF value over one forecast — two answers that must reconcile.</t>
+        </is>
+      </c>
+      <c r="O155" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P155" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q155" s="17" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>Cross-industry — valuation</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>Valuation workbook — DCF, comparables and precedent transactions (worked solution)</t>
+        </is>
+      </c>
+      <c r="E156" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed (training material)</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr"/>
+      <c r="G156" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H156" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J156" s="17" t="inlineStr">
+        <is>
+          <t>Three-method valuation</t>
+        </is>
+      </c>
+      <c r="K156" s="17" t="inlineStr">
+        <is>
+          <t>One business valued by DCF, trading comparables and precedent transactions.</t>
+        </is>
+      </c>
+      <c r="L156" s="17" t="inlineStr">
+        <is>
+          <t>Valuation summary; comparable spread; DCF (two variants); precedent transactions; WACC build.</t>
+        </is>
+      </c>
+      <c r="M156" s="17" t="inlineStr">
+        <is>
+          <t>Other / uncategorised</t>
+        </is>
+      </c>
+      <c r="N156" s="17" t="inlineStr">
+        <is>
+          <t>A WACC build feeding a DCF — the discount rate derived rather than stated.</t>
+        </is>
+      </c>
+      <c r="O156" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P156" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q156" s="17" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>Consumer discretionary — eyewear</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>Luxottica Group — DCF and multiple valuation</t>
+        </is>
+      </c>
+      <c r="E157" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr"/>
+      <c r="G157" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H157" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J157" s="17" t="inlineStr">
+        <is>
+          <t>Listed company DCF with a football-field summary</t>
+        </is>
+      </c>
+      <c r="K157" s="17" t="inlineStr">
+        <is>
+          <t>A listed eyewear manufacturer valued by DCF and multiples.</t>
+        </is>
+      </c>
+      <c r="L157" s="17" t="inlineStr">
+        <is>
+          <t>Beta and WACC build; DCF; multiple valuation; football field; segment detail by geography; consensus comparison; debt outstanding; reorganized balance sheet.</t>
+        </is>
+      </c>
+      <c r="M157" s="17" t="inlineStr">
+        <is>
+          <t>Other / uncategorised</t>
+        </is>
+      </c>
+      <c r="N157" s="17" t="inlineStr">
+        <is>
+          <t>A segment-level build rolling to one enterprise value — multi-entity composition in OpCo.</t>
+        </is>
+      </c>
+      <c r="O157" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P157" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q157" s="17" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>Building materials — cement</t>
+        </is>
+      </c>
+      <c r="D158" s="17" t="inlineStr">
+        <is>
+          <t>Bestway Cement — operating model, three statements and valuation</t>
+        </is>
+      </c>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F158" s="17" t="inlineStr"/>
+      <c r="G158" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H158" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J158" s="17" t="inlineStr">
+        <is>
+          <t>Integrated three-statement model with valuation</t>
+        </is>
+      </c>
+      <c r="K158" s="17" t="inlineStr">
+        <is>
+          <t>A listed cement manufacturer modeled from operations through to value.</t>
+        </is>
+      </c>
+      <c r="L158" s="17" t="inlineStr">
+        <is>
+          <t>Operating model; full financial statements; ratio analysis; valuation; beta and market value.</t>
+        </is>
+      </c>
+      <c r="M158" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N158" s="17" t="inlineStr">
+        <is>
+          <t>A full three-statement linkage — balance sheet and cash flow tying to the income statement.</t>
+        </is>
+      </c>
+      <c r="O158" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P158" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q158" s="17" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>Cross-industry — generic</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>Generic three-statement model with DCF and scenario analysis</t>
+        </is>
+      </c>
+      <c r="E159" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="inlineStr"/>
+      <c r="G159" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H159" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J159" s="17" t="inlineStr">
+        <is>
+          <t>Three-statement model with scenarios</t>
+        </is>
+      </c>
+      <c r="K159" s="17" t="inlineStr">
+        <is>
+          <t>A generic business modeled across scenarios.</t>
+        </is>
+      </c>
+      <c r="L159" s="17" t="inlineStr">
+        <is>
+          <t>P&amp;L, balance sheet and cash flow with separate assumption sheets; DCF valuation; scenarios.</t>
+        </is>
+      </c>
+      <c r="M159" s="17" t="inlineStr">
+        <is>
+          <t>Trigger, covenant &amp; regime switch</t>
+        </is>
+      </c>
+      <c r="N159" s="17" t="inlineStr">
+        <is>
+          <t>Scenario switching over a full statement set — a scenario-harness reference.</t>
+        </is>
+      </c>
+      <c r="O159" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P159" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q159" s="17" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="17" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>OpCo &amp; Corporate Finance (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>Cross-industry — generic</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>Basic DCF template</t>
+        </is>
+      </c>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>business-valuation.net</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="inlineStr"/>
+      <c r="G160" s="17" t="inlineStr">
+        <is>
+          <t>direct download</t>
+        </is>
+      </c>
+      <c r="H160" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>assumptions and outputs only</t>
+        </is>
+      </c>
+      <c r="J160" s="17" t="inlineStr">
+        <is>
+          <t>Minimal DCF</t>
+        </is>
+      </c>
+      <c r="K160" s="17" t="inlineStr">
+        <is>
+          <t>A short DCF with a beta and capital structure sheet.</t>
+        </is>
+      </c>
+      <c r="L160" s="17" t="inlineStr">
+        <is>
+          <t>Free cash flow discounting; beta and capital structure.</t>
+        </is>
+      </c>
+      <c r="M160" s="17" t="inlineStr">
+        <is>
+          <t>Other / uncategorised</t>
+        </is>
+      </c>
+      <c r="N160" s="17" t="inlineStr">
+        <is>
+          <t>A floor case for OpCo discounting, comparable to ID 62 at much smaller scale.</t>
+        </is>
+      </c>
+      <c r="O160" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P160" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="Q160" s="17" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>Energy &amp; Infrastructure (existing pack + roadmap)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>Energy — electricity distribution utility</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>Electricity distribution utility — three-statement model with investor return</t>
+        </is>
+      </c>
+      <c r="E161" s="17" t="inlineStr">
+        <is>
+          <t>Unattributed</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr"/>
+      <c r="G161" s="17" t="inlineStr">
+        <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="H161" s="17" t="inlineStr">
+        <is>
+          <t>Provenance not established; treat as not redistributable</t>
+        </is>
+      </c>
+      <c r="I161" s="17" t="inlineStr">
+        <is>
+          <t>full cash flow table available</t>
+        </is>
+      </c>
+      <c r="J161" s="17" t="inlineStr">
+        <is>
+          <t>Regulated distribution utility financial model</t>
+        </is>
+      </c>
+      <c r="K161" s="17" t="inlineStr">
+        <is>
+          <t>An electricity distribution business modeled from drivers through to investor return.</t>
+        </is>
+      </c>
+      <c r="L161" s="17" t="inlineStr">
+        <is>
+          <t>Driver sheet; income statement, balance sheet and cash flow; ratio analysis; valuation; investor return; capex; capital structure.</t>
+        </is>
+      </c>
+      <c r="M161" s="17" t="inlineStr">
+        <is>
+          <t>Composition, nesting &amp; multi-entity</t>
+        </is>
+      </c>
+      <c r="N161" s="17" t="inlineStr">
+        <is>
+          <t>A regulated utility — a rate-base business, unlike the merchant and PPA cases in the pack.</t>
+        </is>
+      </c>
+      <c r="O161" s="17" t="inlineStr">
+        <is>
+          <t>n/a — local file</t>
+        </is>
+      </c>
+      <c r="P161" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="Q161" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O107"/>
@@ -18191,7 +22298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="56" customWidth="1" style="17" min="1" max="1"/>
@@ -18231,7 +22338,7 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>COUNTIF('Model Catalogue'!$B$2:$B$108,A5)</f>
+        <f>COUNTIF('Model Catalogue'!$B$2:$B$161,A5)</f>
         <v/>
       </c>
     </row>
@@ -18242,7 +22349,7 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>COUNTIF('Model Catalogue'!$B$2:$B$108,A6)</f>
+        <f>COUNTIF('Model Catalogue'!$B$2:$B$161,A6)</f>
         <v/>
       </c>
     </row>
@@ -18253,7 +22360,7 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>COUNTIF('Model Catalogue'!$B$2:$B$108,A7)</f>
+        <f>COUNTIF('Model Catalogue'!$B$2:$B$161,A7)</f>
         <v/>
       </c>
     </row>
@@ -18264,7 +22371,7 @@
         </is>
       </c>
       <c r="B8" s="34">
-        <f>COUNTIF('Model Catalogue'!$B$2:$B$108,A8)</f>
+        <f>COUNTIF('Model Catalogue'!$B$2:$B$161,A8)</f>
         <v/>
       </c>
     </row>
@@ -18275,7 +22382,7 @@
         </is>
       </c>
       <c r="B9" s="34">
-        <f>COUNTIF('Model Catalogue'!$B$2:$B$108,A9)</f>
+        <f>COUNTIF('Model Catalogue'!$B$2:$B$161,A9)</f>
         <v/>
       </c>
     </row>
@@ -18316,7 +22423,7 @@
         </is>
       </c>
       <c r="B14" s="34">
-        <f>COUNTIF('Model Catalogue'!$G$2:$G$108,A14)</f>
+        <f>COUNTIF('Model Catalogue'!$G$2:$G$161,A14)</f>
         <v/>
       </c>
     </row>
@@ -18327,7 +22434,7 @@
         </is>
       </c>
       <c r="B15" s="34">
-        <f>COUNTIF('Model Catalogue'!$G$2:$G$108,A15)</f>
+        <f>COUNTIF('Model Catalogue'!$G$2:$G$161,A15)</f>
         <v/>
       </c>
     </row>
@@ -18338,7 +22445,7 @@
         </is>
       </c>
       <c r="B16" s="34">
-        <f>COUNTIF('Model Catalogue'!$G$2:$G$108,A16)</f>
+        <f>COUNTIF('Model Catalogue'!$G$2:$G$161,A16)</f>
         <v/>
       </c>
     </row>
@@ -18349,18 +22456,29 @@
         </is>
       </c>
       <c r="B17" s="34">
-        <f>COUNTIF('Model Catalogue'!$G$2:$G$108,A17)</f>
+        <f>COUNTIF('Model Catalogue'!$G$2:$G$161,A17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="18">
       <c r="A18" s="33" t="inlineStr">
         <is>
+          <t>private corpus (not redistributable)</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f>COUNTIF('Model Catalogue'!$G$2:$G$161,A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" s="33">
-        <f>SUM(B14:B17)</f>
+      <c r="B19" s="17">
+        <f>SUM(B14:B18)</f>
         <v/>
       </c>
     </row>
@@ -18390,7 +22508,7 @@
         </is>
       </c>
       <c r="B22" s="34">
-        <f>COUNTIF('Model Catalogue'!$I$2:$I$108,A22)</f>
+        <f>COUNTIF('Model Catalogue'!$I$2:$I$161,A22)</f>
         <v/>
       </c>
     </row>
@@ -18401,7 +22519,7 @@
         </is>
       </c>
       <c r="B23" s="34">
-        <f>COUNTIF('Model Catalogue'!$I$2:$I$108,A23)</f>
+        <f>COUNTIF('Model Catalogue'!$I$2:$I$161,A23)</f>
         <v/>
       </c>
     </row>
@@ -18412,7 +22530,7 @@
         </is>
       </c>
       <c r="B24" s="34">
-        <f>COUNTIF('Model Catalogue'!$I$2:$I$108,A24)</f>
+        <f>COUNTIF('Model Catalogue'!$I$2:$I$161,A24)</f>
         <v/>
       </c>
     </row>
@@ -18753,6 +22871,69 @@
         <is>
           <t>Note: access and fidelity labels are as recorded by the researcher; a small number of entries use wording that does not match a bucket exactly and will show as zero above. Filter the Model Catalogue sheet directly for the authoritative view.</t>
         </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Model catalogue by local copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Local copy</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>public template</t>
+        </is>
+      </c>
+      <c r="B64" s="17">
+        <f>COUNTIF('Model Catalogue'!$P$2:$P$161,A64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>private corpus</t>
+        </is>
+      </c>
+      <c r="B65" s="17">
+        <f>COUNTIF('Model Catalogue'!$P$2:$P$161,A65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>no local copy (sourced by URL)</t>
+        </is>
+      </c>
+      <c r="B66" s="17">
+        <f>COUNTBLANK('Model Catalogue'!$P$2:$P$161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B67" s="17">
+        <f>SUM(B64:B66)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
